--- a/data/600733_北汽蓝谷_财务数据.xlsx
+++ b/data/600733_北汽蓝谷_财务数据.xlsx
@@ -10785,7 +10785,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -17582,7 +17582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -17612,8 +17612,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17660,22 +17658,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -17685,75 +17683,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -17788,53 +17776,49 @@
       </c>
       <c r="I2" s="4" t="inlineStr"/>
       <c r="J2" s="3" t="n">
-        <v>-1.176332393341019</v>
+        <v>38.27493261455525</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>38.27493261455525</v>
-      </c>
-      <c r="L2" s="3" t="n">
         <v>3.063751206614345</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="L2" s="6" t="n">
         <v>0.8603684895286859</v>
       </c>
+      <c r="M2" s="3" t="n">
+        <v>61.73913043478262</v>
+      </c>
       <c r="N2" s="4" t="inlineStr"/>
-      <c r="O2" s="4" t="inlineStr"/>
+      <c r="O2" s="6" t="n">
+        <v>0.0560175640952381</v>
+      </c>
       <c r="P2" s="6" t="n">
-        <v>0.0560175640952381</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>6426.555774327263</v>
-      </c>
-      <c r="R2" s="6" t="n">
         <v>0.0144679548787062</v>
       </c>
-      <c r="S2" s="6" t="n">
+      <c r="Q2" s="6" t="n">
         <v>0.01838223034246575</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
+      <c r="V2" s="3" t="n">
+        <v>1.942849215283969</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>-84164600</v>
+      </c>
       <c r="X2" s="3" t="n">
-        <v>1.942849215283969</v>
-      </c>
-      <c r="Y2" s="3" t="n">
-        <v>-84164600</v>
+        <v>1.1076994424518</v>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>−/+/+</t>
+        </is>
       </c>
       <c r="Z2" s="3" t="n">
-        <v>1.1076994424518</v>
+        <v>1.024669008945142</v>
       </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>−/+/+</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>1.024669008945142</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -17870,64 +17854,58 @@
       <c r="I3" s="6" t="n">
         <v>0.1317877998462167</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>-0.6827027029781779</v>
+      <c r="J3" s="3" t="n">
+        <v>42.63699231228279</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>42.63699231228279</v>
+        <v>1.979610496479839</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1.979610496479839</v>
+        <v>1.91185882783213</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>1.91185882783213</v>
+        <v>74.32837647634784</v>
       </c>
       <c r="N3" s="6" t="n">
         <v>0.8204911353133922</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>438.7615959586151</v>
-      </c>
-      <c r="P3" s="3" t="n">
         <v>24.10794569512093</v>
       </c>
+      <c r="P3" s="6" t="n">
+        <v>0.7965513773282972</v>
+      </c>
       <c r="Q3" s="3" t="n">
-        <v>14.93283602645822</v>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v>0.7965513773282972</v>
-      </c>
+        <v>1.047572330444333</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.047572330444333</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>214025.7864391245</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>194.350502166467</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>214025.7864391245</v>
+        <v>7578.436657681941</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>194.350502166467</v>
+        <v>-105.8773062327833</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>7578.436657681941</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>-105.8773062327833</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>-5411000000</v>
       </c>
-      <c r="Z3" s="6" t="n">
+      <c r="X3" s="6" t="n">
         <v>0.7599987587843658</v>
       </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>1.667708149874749</v>
+      </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>1.667708149874749</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -17963,64 +17941,58 @@
       <c r="I4" s="3" t="n">
         <v>1.962587346990027</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>0.6035545073873139</v>
+      <c r="J4" s="3" t="n">
+        <v>63.0345853477129</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>63.0345853477129</v>
+        <v>1.462405699916178</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.462405699916178</v>
+        <v>1.43558256496228</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1.43558256496228</v>
+        <v>170.523138832998</v>
       </c>
       <c r="N4" s="6" t="n">
         <v>0.930989793801302</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>386.6852272677369</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>27.30706499960898</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>13.18340143860774</v>
-      </c>
-      <c r="R4" s="6" t="n">
+      <c r="P4" s="6" t="n">
         <v>0.487615314777628</v>
       </c>
-      <c r="S4" s="6" t="n">
+      <c r="Q4" s="6" t="n">
         <v>0.6398743696324986</v>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
+      <c r="R4" s="4" t="inlineStr"/>
+      <c r="S4" s="3" t="n">
+        <v>57.39872880622318</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-182.4792001340317</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>57.39872880622318</v>
+        <v>60.46968792782673</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-182.4792001340317</v>
+        <v>104.2493377227811</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>60.46968792782673</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>104.2493377227811</v>
-      </c>
-      <c r="Y4" s="3" t="n">
         <v>-4979000000</v>
       </c>
-      <c r="Z4" s="6" t="n">
+      <c r="X4" s="6" t="n">
         <v>0.4490747821153931</v>
       </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1.034816317876334</v>
+      </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>1.034816317876334</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18057,63 +18029,57 @@
         <v>1.859196511580942</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.047269751009275</v>
+        <v>70.15016233766234</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>70.15016233766234</v>
+        <v>1.501928104575163</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.501928104575163</v>
+        <v>1.313954248366013</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.313954248366013</v>
+        <v>235.0101971447995</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>1.014240980236053</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>354.9452319666813</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>7.775832536974343</v>
       </c>
-      <c r="Q5" s="3" t="n">
-        <v>46.2972933493858</v>
-      </c>
-      <c r="R5" s="6" t="n">
+      <c r="P5" s="6" t="n">
         <v>0.4499558335862049</v>
       </c>
-      <c r="S5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>0.5835034284331866</v>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
+      <c r="R5" s="4" t="inlineStr"/>
+      <c r="S5" s="3" t="n">
+        <v>30.39259752625902</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>111.537097124307</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>30.39259752625902</v>
+        <v>29.36363835232866</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>111.537097124307</v>
+        <v>-1640.059158255554</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>29.36363835232866</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>-1640.059158255554</v>
-      </c>
-      <c r="Y5" s="3" t="n">
         <v>-8976000000</v>
       </c>
+      <c r="X5" s="6" t="n">
+        <v>0.4776861554576857</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
       <c r="Z5" s="6" t="n">
-        <v>0.4776861554576857</v>
+        <v>0.9875747922765893</v>
       </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB5" s="6" t="n">
-        <v>0.9875747922765893</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18150,63 +18116,57 @@
         <v>18.45798270598754</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>15.27812544514401</v>
+        <v>73.90546921560536</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>73.90546921560536</v>
+        <v>1.362362776170135</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1.362362776170135</v>
+        <v>1.174819714298838</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>1.174819714298838</v>
+        <v>283.2220660576247</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>0.2605488347776241</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1381.698752586081</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>2.108351543011693</v>
       </c>
-      <c r="Q6" s="3" t="n">
-        <v>170.7495133784734</v>
-      </c>
-      <c r="R6" s="6" t="n">
+      <c r="P6" s="6" t="n">
         <v>0.1026150954742025</v>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>0.139448186846163</v>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="3" t="n">
+        <v>-77.64834825452768</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-166636.2013158577</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>-77.64834825452768</v>
+        <v>-26.22767857142857</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>-166636.2013158577</v>
+        <v>1.022327239287919</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-26.22767857142857</v>
+        <v>-7693999999.999999</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>1.022327239287919</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>-7693999999.999999</v>
-      </c>
-      <c r="Z6" s="3" t="n">
         <v>1.517126836926498</v>
       </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>−/+/+</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="n">
+        <v>-0.08699798924413736</v>
+      </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>−/+/+</t>
-        </is>
-      </c>
-      <c r="AB6" s="6" t="n">
-        <v>-0.08699798924413736</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18243,63 +18203,57 @@
         <v>13.89192893222767</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7.555802589929825</v>
+        <v>70.10056037460657</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>70.10056037460657</v>
+        <v>1.306728197598196</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.306728197598196</v>
+        <v>1.241491425874456</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.241491425874456</v>
+        <v>234.4544287548138</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>0.5296806182678604</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>679.654847816137</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>4.884522042879669</v>
       </c>
-      <c r="Q7" s="3" t="n">
-        <v>73.70219580128295</v>
-      </c>
-      <c r="R7" s="6" t="n">
+      <c r="P7" s="6" t="n">
         <v>0.2103044741397947</v>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="Q7" s="6" t="n">
         <v>0.3186934688460552</v>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="3" t="n">
+        <v>64.94797135781917</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>20.17355746743534</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>64.94797135781917</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>20.17355746743534</v>
+        <v>-10.41809929858341</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>-0.9642390859625147</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>-10.41809929858341</v>
-      </c>
-      <c r="X7" s="6" t="n">
-        <v>-0.9642390859625147</v>
-      </c>
-      <c r="Y7" s="3" t="n">
         <v>2723000000</v>
       </c>
-      <c r="Z7" s="3" t="n">
+      <c r="X7" s="3" t="n">
         <v>1.612657294161459</v>
       </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="n">
+        <v>-0.1442913523316486</v>
+      </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB7" s="6" t="n">
-        <v>-0.1442913523316486</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18336,63 +18290,57 @@
         <v>13.12734323127247</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>5.887781898626572</v>
-      </c>
-      <c r="K8" s="3" t="n">
         <v>79.89539482076795</v>
       </c>
+      <c r="K8" s="6" t="n">
+        <v>0.9056307837088932</v>
+      </c>
       <c r="L8" s="6" t="n">
-        <v>0.9056307837088932</v>
-      </c>
-      <c r="M8" s="6" t="n">
         <v>0.7430334082710305</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>397.4615262573378</v>
       </c>
       <c r="N8" s="6" t="n">
         <v>0.8695184032736246</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>414.0222894014048</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>6.719320477795131</v>
       </c>
-      <c r="Q8" s="3" t="n">
-        <v>53.5768462286725</v>
-      </c>
-      <c r="R8" s="6" t="n">
+      <c r="P8" s="6" t="n">
         <v>0.2701497897020032</v>
       </c>
-      <c r="S8" s="6" t="n">
+      <c r="Q8" s="6" t="n">
         <v>0.4504862863929925</v>
       </c>
-      <c r="T8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>9.399340524629459</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-4.370526670007965</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>9.399340524629459</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-4.370526670007965</v>
+        <v>-19.76663851999693</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>-0.6527262007849755</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>-19.76663851999693</v>
-      </c>
-      <c r="X8" s="6" t="n">
-        <v>-0.6527262007849755</v>
-      </c>
-      <c r="Y8" s="3" t="n">
         <v>1461000000</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="X8" s="3" t="n">
         <v>1.503005427212192</v>
       </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z8" s="6" t="n">
+        <v>-0.8924703665922589</v>
+      </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB8" s="6" t="n">
-        <v>-0.8924703665922589</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18429,63 +18377,57 @@
         <v>8.279484753198506</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>2.915102033248539</v>
-      </c>
-      <c r="K9" s="3" t="n">
         <v>77.40982435635206</v>
       </c>
+      <c r="K9" s="6" t="n">
+        <v>0.7977095316351686</v>
+      </c>
       <c r="L9" s="6" t="n">
-        <v>0.7977095316351686</v>
-      </c>
-      <c r="M9" s="6" t="n">
         <v>0.7126129827444537</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>342.6210662451502</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>1.95222758475288</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>184.4047296594111</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>8.257604706280679</v>
       </c>
-      <c r="Q9" s="3" t="n">
-        <v>43.59617743946818</v>
-      </c>
-      <c r="R9" s="6" t="n">
+      <c r="P9" s="6" t="n">
         <v>0.4607240767852374</v>
       </c>
-      <c r="S9" s="6" t="n">
+      <c r="Q9" s="6" t="n">
         <v>0.8716246063229341</v>
       </c>
-      <c r="T9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="3" t="n">
+        <v>50.49617748509334</v>
+      </c>
+      <c r="T9" s="6" t="n">
+        <v>0.5621999088631201</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>50.49617748509334</v>
+        <v>-1.769996172981247</v>
       </c>
       <c r="V9" s="6" t="n">
-        <v>0.5621999088631201</v>
+        <v>0.08666487989424106</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>-1.769996172981247</v>
+        <v>-2711000000</v>
       </c>
       <c r="X9" s="6" t="n">
-        <v>0.08666487989424106</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>-2711000000</v>
-      </c>
-      <c r="Z9" s="6" t="n">
         <v>0.9921351866527274</v>
       </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>-1.066222061175884</v>
+      </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>-1.066222061175884</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18522,63 +18464,57 @@
         <v>12.13110371817378</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.647012527964995</v>
+        <v>75.32652519253519</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>75.32652519253519</v>
-      </c>
-      <c r="L10" s="3" t="n">
         <v>1.030419373892498</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="L10" s="6" t="n">
         <v>0.9591173740612606</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>305.293542074364</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>1.800820103452255</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>199.9089188919334</v>
-      </c>
-      <c r="P10" s="3" t="n">
         <v>12.65342295848222</v>
       </c>
-      <c r="Q10" s="3" t="n">
-        <v>28.4507995331551</v>
-      </c>
-      <c r="R10" s="6" t="n">
+      <c r="P10" s="6" t="n">
         <v>0.4018694803154164</v>
       </c>
-      <c r="S10" s="6" t="n">
+      <c r="Q10" s="6" t="n">
         <v>0.7263944741050156</v>
       </c>
-      <c r="T10" s="4" t="inlineStr"/>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="3" t="n">
+        <v>1.349960225373029</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>-28.09455176453712</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>1.349960225373029</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>-28.09455176453712</v>
+        <v>34.47940001947989</v>
+      </c>
+      <c r="V10" s="6" t="n">
+        <v>0.2287241750974963</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>34.47940001947989</v>
+        <v>-4128000000</v>
       </c>
       <c r="X10" s="6" t="n">
-        <v>0.2287241750974963</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>-4128000000</v>
+        <v>0.6539456751271768</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
       </c>
       <c r="Z10" s="6" t="n">
-        <v>0.6539456751271768</v>
+        <v>-0.9444560924832894</v>
       </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB10" s="6" t="n">
-        <v>-0.9444560924832894</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18614,64 +18550,58 @@
       <c r="I11" s="3" t="n">
         <v>8.038486085624401</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>0.4088244938759943</v>
-      </c>
-      <c r="K11" s="3" t="n">
+      <c r="J11" s="3" t="n">
         <v>88.47276844237874</v>
       </c>
+      <c r="K11" s="6" t="n">
+        <v>0.6540868127976074</v>
+      </c>
       <c r="L11" s="6" t="n">
-        <v>0.6540868127976074</v>
-      </c>
-      <c r="M11" s="6" t="n">
         <v>0.5880917712801542</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>767.5109847505815</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>3.481426238948352</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>103.4058961159397</v>
-      </c>
-      <c r="P11" s="3" t="n">
         <v>20.1727746821384</v>
       </c>
+      <c r="P11" s="6" t="n">
+        <v>0.7452206782871241</v>
+      </c>
       <c r="Q11" s="3" t="n">
-        <v>17.84583458014604</v>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>0.7452206782871241</v>
-      </c>
+        <v>1.361474821200663</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.361474821200663</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>92.53281328238533</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>7.142411138603817</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>92.53281328238533</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>7.142411138603817</v>
+        <v>-18.96863909611067</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>-0.3030390496991659</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>-18.96863909611067</v>
+        <v>-1180000000</v>
       </c>
       <c r="X11" s="6" t="n">
-        <v>-0.3030390496991659</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>-1180000000</v>
-      </c>
-      <c r="Z11" s="6" t="n">
         <v>0.8544681757010448</v>
       </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>-1.443605603960012</v>
+      </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>-1.443605603960012</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>

--- a/data/600733_北汽蓝谷_财务数据.xlsx
+++ b/data/600733_北汽蓝谷_财务数据.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务分析指标" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据质量校验" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合并报表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="财务指标表" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37560,4 +37561,2123 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>毛利率</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>营业利润率</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>净利润率</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>净资产收益率</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>存货周转率</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>总资产周转率</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>应收账款周转率</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>流动比率</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>速动比率</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>利息保障倍数</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>资产负债率</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>货币资金占比</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>营业收入增长率</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>营业利润增长率</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>净利润增长率</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2016Q1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.6860176633587407</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.6162452981065503</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.6195985756053971</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.01081195556109726</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03572504569377991</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01105743610486891</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.111111111111111</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.185116666666667</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3697674418604651</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1718481395348837</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.1749582923410142</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.4811034319931818</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-0.9366527780894888</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2016Q2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>-1.0521686312739</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.9965185493520481</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.114053398361019</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.01907537758139535</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.04735541287081339</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01125516956826138</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.427536231884058</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9057434782608695</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.3747072599531617</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1661381733021078</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.08904521138469734</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.7610742955157286</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9581299352188954</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2016Q3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-1.487467640673951</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.404786612667181</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.640489456276678</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.02931179737089202</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05933180095238095</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01188370348754448</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.511627906976744</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8796271317829457</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.3629807692307692</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1612596153846154</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.03859569337251245</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4641025267137897</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.529374881687529</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2017年报</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.002619898472736581</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.002258540558675224</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.00355577265359201</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.007191445748184019</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24.10794569512093</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7953112011535134</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.627407234801956</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.979610496479839</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.905747307305477</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.712500498336365</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.426369923122828</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.208305542879208</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2293.566455248817</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-4.689080858989426</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-5.973489236524078</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2017Q1</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.03570167325794382</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.01386533530866864</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.01386533530866864</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4.362474868125871e-05</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.02174075052410902</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0006937718392516889</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.003160126896007575</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.009803921568627</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9163911764705882</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.3941798941798942</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.1577925925925926</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.9991288193766367</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1.005348237564719</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1.003397070801235</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017Q2</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.2944347019121869</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.2900456800419521</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2904554981538035</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.009026417554347826</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.06185630084507043</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.02699865010610079</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.970873786407767</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8977854368932039</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.398936170212766</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1569936170212766</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0165416260447897</v>
+      </c>
+      <c r="O7" t="n">
+        <v>20.26479458688431</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20.29484053676794</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2017Q3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.01258965153427349</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.01425234437585148</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.01133814317487784</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.4612458255434783</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27.66873235401869</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15.7597999394481</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.90990990990991</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9682153153153154</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.405186632683185</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.4077922077922078</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1662238961038961</v>
+      </c>
+      <c r="N8" t="n">
+        <v>588.1446800844034</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-29.94955327915682</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-23.99769422845436</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2018年报</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.04228733381592198</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.001760848348712032</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.001863276066783183</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.008752601018689915</v>
+      </c>
+      <c r="F9" t="n">
+        <v>44.1064991397193</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7848725835502625</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.008050635836386</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.462405699916178</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.431751684828164</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.630345853477129</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1368100977840002</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.016795597881156</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1.372719000246119</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-1.495771040214386</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2018Q1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.1343801099623674</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.1290571095292299</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.1289954635135348</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.02683371788323782</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.670324236964079</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.07708567362839538</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1971935214163614</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.115384615384615</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9710826923076923</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-382.2218896995529</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3905013192612137</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2294944591029024</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.9017985314228757</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6.197438493416671</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.798533069061322</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2018Q2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.02087106604988875</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.01310580239169586</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01386287550272331</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4618148819148936</v>
+      </c>
+      <c r="F11" t="n">
+        <v>24.76389947187905</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14.12739212186163</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.472602739726027</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8287164383561644</v>
+      </c>
+      <c r="K11" t="n">
+        <v>12.23307476879477</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4567307692307692</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2296456730769231</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.161039357460367</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1.321004842913097</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1.339710357853659</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2018Q3</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-0.01313131704739989</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.008299164409440948</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01288344855400265</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.01613895890871445</v>
+      </c>
+      <c r="F12" t="n">
+        <v>16.28190496648604</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5847794819705434</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.988856289372079</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.803098131173168</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.725573793789526</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.601644380611531</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5092718637504916</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1256919865686541</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.7428404676134499</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.1036424285868798</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.6197069286181527</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2019年报</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.05353625577066912</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.006981694436353588</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0001648620961596009</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.005473532618679357</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.385307812234769</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5117245256763528</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.560719174132592</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.501928104575163</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.292091503267974</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7357620270468598</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7015016233766234</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1516673430735931</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.410168553445188</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-3.027560794086757</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.9691584564370788</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2019Q1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-0.06648106163555578</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.001135174285870032</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.000990988470342751</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.001215226451761588</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.044944909122227</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0682529385551652</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1748630114059465</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.469056505511674</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.376486416109713</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.9588328385552859</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6157364237822477</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.09309089294436304</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.8492826705227847</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.9754944249684331</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.09403592898529445</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2019Q2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>-0.03884776783069999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.003332913163293239</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.003143567737107092</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.003953419706780344</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.659341418374266</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.212627957700202</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4774413157817778</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.388339210517306</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.269505974186039</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.155838313318126</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6660834454912516</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.1103249375120169</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.902201000696609</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-9.520968135153824</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8.206227625669888</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2019Q3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-0.08112947150335859</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.02283209248905706</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.0207319559437384</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.01821570628853697</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.619624673505474</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.3262733298194638</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8161913074359616</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.515145593120969</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.324864829652791</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.03466136368062734</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.7071712804258324</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.1409105786291364</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.7401639697695257</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-12.9209780625199</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-12.47645152680662</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2020年报</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>-0.9664078021648872</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.244064393395644</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-1.228343549194352</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.4639261584606026</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.208032949155574</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1037101059346755</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.268196053744341</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.362362776170135</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.169583390749162</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-5.742238125003397</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7390546921560537</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.09100077935176271</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0.7063508338075937</v>
+      </c>
+      <c r="O17" t="n">
+        <v>15.00021863897854</v>
+      </c>
+      <c r="P17" t="n">
+        <v>16.39836125436511</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2020Q1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.3374950660148315</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.2926225836624588</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.2597367807686011</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.03090485772836495</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4379114105165979</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.03257798294380924</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.08473438717535521</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.5365820642978</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.307174280879865</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1.132260248002281</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.7049434450804034</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1420175797219951</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-0.6838571500334885</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-0.9256384652959093</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-0.9331506839701568</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2020Q2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.4682380025184341</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.6371464131337614</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.599624427014091</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.1146525423783152</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.7888270978420371</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05595815227287847</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1500667691956794</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.657999830062027</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.411292378281927</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-2.935930259890716</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6955164207520228</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1090337934316992</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.8670426234976847</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.065234801226353</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3.310226530154257</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2020Q3</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.6770680310906345</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.7795166442251203</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.7351191354686916</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-0.1919071900066538</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.221686031581685</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.07660979034840448</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1927737839029665</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.645019060304046</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.390851054057778</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-3.166035426388026</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6996349486521181</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.1317594672657253</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.260149996484756</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5417302463474281</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5449009984294375</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2021年报</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.4959393639115792</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.5954685975606814</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-0.5944559059007867</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.4090472277397715</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3.987716309949425</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1955727328634876</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5255038563908275</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.306728197598196</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.234936284021186</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-6.080358473425346</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.7010056037460659</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.1695708912259154</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.217620048989738</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.6940281009740807</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.7932839339373809</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2021Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-1.005214024998616</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.014363495365125</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.017066066657062</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.08060024689290603</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5978373187935367</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.02031994620715815</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.05735666783338514</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.334310568558658</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.120151871966165</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-3.257192429903546</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.7528843448081793</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.09168933495919708</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.9045256516482151</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.8373622150545814</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.8366510972791943</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2021Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.8085900704254814</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.7365408175672257</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.7432532162243116</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.1472714411986844</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.175799303662798</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.05623890109571338</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1521823574939895</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.608844476342958</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.425881963230829</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-3.680169176864084</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.658662910883442</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1508825333363622</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.934966065266242</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.131112086663903</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.144819337733236</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2021Q3</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.4752849324966497</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.4293054764198522</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.4320389901018708</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.1869779562528728</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.738286699837939</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1419378014661794</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4033824056750678</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.655058043117745</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.543578404274922</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-3.714137084905348</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6612891678400115</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1520893492112737</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.50225746206963</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4584837747717703</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.4545147781253178</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2022年报</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.5374758245683231</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.5701863480790337</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.5671302558445834</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.563622913072401</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6.156549107811448</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.2597433863039354</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.9052157717159032</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9056307837088932</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.7316359073560935</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-7.268823184947295</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.7989539482076795</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.156301824212272</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.5602454470109151</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.072255543900987</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.048107739847749</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2022Q1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>-0.6050967118844495</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.5459339443676625</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-0.5465755614037401</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.1208696557688664</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.395831237663316</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.04828079071770335</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1808404328428863</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.234553399426773</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.187097683597237</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-4.087369841629002</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.7336788078649178</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.2370385063598721</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.8181098019037052</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.8258463507183765</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.8247021101170733</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2022Q2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-0.6347579711007612</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.6103557970724722</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-0.6253322525220542</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.2281332742840707</v>
+      </c>
+      <c r="F27" t="n">
+        <v>5.614417631599211</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.08894073367683714</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3097582877505231</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.098105263157895</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.021473684210526</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-4.989217221713268</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.7486412326526305</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.2494327476122632</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.010369615750424</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.247599296381673</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.300046048510552</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2022Q3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.6289280027706921</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.6048232562415661</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.6089540825448114</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.4217456400204869</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5.200514180581819</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1564484745576665</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.5765871186097499</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.077474438705597</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9193106356066196</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-5.689422798668703</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.7652345087298871</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.166267260070752</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.6403244172476505</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.6254557752885124</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.5973624366123145</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2023年报</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-0.3745745146198876</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.3735954691017046</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-0.3747217102035356</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.7752740479569276</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9.657507761246318</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.4348659353520721</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.931684751483305</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7977095316351684</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6949465899753492</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-9.296695643855504</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.7740982435635206</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.1897665660205838</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.509056908751319</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.5498284550973616</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.5439556491947877</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2023Q1</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-0.4452933851342304</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.3548549649735948</v>
+      </c>
+      <c r="D30" t="n">
+        <v>-0.3545377429035698</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.1617292667428364</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.557775709451878</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.08040581857142858</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4408339486337158</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9178970111631257</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.7499356962806729</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-6.00942157043496</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.8283041159753488</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.172174857106364</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.8255889533032956</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-0.8343378574280342</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-0.8349834099558525</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2023Q2</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.416205081691585</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.3429223782953995</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-0.3407813557545089</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.2741568710960327</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3.034356587994802</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1801749721316492</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.005141258606393</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.185693377241127</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.021527015489694</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-6.649478034952813</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.6837040205303678</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.2430648906269094</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.310478199050003</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.23278453797837</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.220829541772231</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2023Q3</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.3942187345758086</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.3486717511533992</v>
+      </c>
+      <c r="D32" t="n">
+        <v>-0.3472660067007902</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.3584877775667034</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5.22745204286002</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.2849829794139799</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.758184565666792</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.126078132927448</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9350583460172501</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-7.445819750922114</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.7211721386928506</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.1784596501994477</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.6131382118899926</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.6401837873282139</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.6438342521972875</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2024年报</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.4591811185903267</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.4671494731613501</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.4736046210400572</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.9965591765289731</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9.97433034433349</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.392155458071638</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.886793078112194</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.030419373892498</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9453210699519028</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-14.81579956772424</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.7532652519253519</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2861350522681732</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.5591077857524533</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.088888412401336</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.126325749666914</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2024Q1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.6596938141172828</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.6646871056684412</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-0.6643475156767037</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-0.1885177267415105</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.215495720136286</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.04239368137749352</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3330684093967903</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7440885020709904</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.5936140093325644</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-8.180959400953284</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.7986672529851504</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.1612826844366269</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.8963171172168968</v>
+      </c>
+      <c r="O34" t="n">
+        <v>-0.8524740383456286</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-0.8545591353313093</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2024Q2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.6523319766992133</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.676826052442396</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.6763502277715434</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.5723104356799467</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.561287930532422</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.1265600456768323</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.8026557026882644</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.6091800780878012</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.473383487286925</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-10.92852690690297</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.8502266729819338</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.07794844035455714</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.48643318977056</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.531842044388352</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.531355374343601</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2024Q3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.4374157341873197</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.4514476587698268</v>
+      </c>
+      <c r="D36" t="n">
+        <v>-0.4512311724092311</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-1.628821705515866</v>
+      </c>
+      <c r="F36" t="n">
+        <v>6.296270928324782</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.3145958180672551</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.997432241678364</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6888273714260997</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.5732081837449716</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-12.75991636113766</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.9231307629104409</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.1130823772861447</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.624408028634975</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.7504983088469865</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.7508897949852706</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025年报</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.2154846011482452</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.2285393480513543</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.2284170808790569</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-3.322412337779395</v>
+      </c>
+      <c r="F37" t="n">
+        <v>18.10280713079957</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8412551382967256</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6.414920509856503</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.6540868127976074</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.5647947739168077</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-34.67943232355398</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.8847276844237874</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.1814444047193421</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.845702799093298</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.4405990369401467</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.4405191089695979</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025Q1</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.3644457254396758</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.3587858661990175</v>
+      </c>
+      <c r="D38" t="n">
+        <v>-0.3599426642601573</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.3464467396366279</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.719435028452192</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1091753105301233</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.8988398764264444</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.8968824940047961</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.7801438848920863</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-23.90180789242855</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.7508157065706571</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.2210283528352835</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.8649658114874896</v>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.7880086790085014</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-0.7872113355430865</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025Q2</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.3197365043253957</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.3445830476713879</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-0.3457471732083143</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.5950435064114462</v>
+      </c>
+      <c r="F39" t="n">
+        <v>5.949648930999526</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.2693620534346607</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.461037163149729</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.7760456926908872</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6694150992012368</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-33.23665718782501</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.8025918541726004</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.235431500996867</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.522431073370219</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.42257867070155</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.422950930318777</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025Q3</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.2881435221259234</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.3091210424837545</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-0.3084373643123983</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-1.294909367405027</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9.960851165096757</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.4462175750088465</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5.053126402883889</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.6907463439233484</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.5868213145066398</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-34.29380795888377</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.8381396997990781</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.1623035102233779</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.6165301036169901</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.4501684694396184</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.4420892580685389</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/600733_北汽蓝谷_财务数据.xlsx
+++ b/data/600733_北汽蓝谷_财务数据.xlsx
@@ -37569,7 +37569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37648,6 +37648,21 @@
           <t>净利润增长率</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>有息负债率</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>经营现金流/营收</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>权益乘数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37700,6 +37715,15 @@
       <c r="P2" t="n">
         <v>-0.9366527780894888</v>
       </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-7.656379317114453</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.990740740740741</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37752,6 +37776,15 @@
       <c r="P3" t="n">
         <v>0.9581299352188954</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-7.702909233467111</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.995327102803738</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -37804,6 +37837,15 @@
       <c r="P4" t="n">
         <v>0.529374881687529</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-9.577237328002493</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.962264150943396</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -37856,6 +37898,15 @@
       <c r="P5" t="n">
         <v>-5.973489236524078</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0.001308442447432162</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0.3764756301385175</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.746811380917341</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -37908,6 +37959,15 @@
       <c r="P6" t="n">
         <v>-1.003397070801235</v>
       </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-3.536091853904864</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.043243243243243</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -37960,6 +38020,15 @@
       <c r="P7" t="n">
         <v>20.29484053676794</v>
       </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-3.549966265186366</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.054644808743169</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -38012,6 +38081,15 @@
       <c r="P8" t="n">
         <v>-23.99769422845436</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-0.638027803487264</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.081081081081081</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -38064,6 +38142,15 @@
       <c r="P9" t="n">
         <v>-1.495771040214386</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.1578867390020344</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-0.1942452959568552</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.760113512860765</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -38116,6 +38203,15 @@
       <c r="P10" t="n">
         <v>5.798533069061322</v>
       </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-0.7362723894036547</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.994736842105263</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -38168,6 +38264,15 @@
       <c r="P11" t="n">
         <v>-1.339710357853659</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-0.6857635316481021</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.236559139784946</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -38220,6 +38325,15 @@
       <c r="P12" t="n">
         <v>0.6197069286181527</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0.1508539885652055</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-0.436796702390268</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.03615645210964</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -38272,6 +38386,15 @@
       <c r="P13" t="n">
         <v>-0.9691584564370788</v>
       </c>
+      <c r="Q13" t="n">
+        <v>0.345221185064935</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0.2703835906557614</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.401553062985332</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -38324,6 +38447,15 @@
       <c r="P14" t="n">
         <v>-0.09403592898529445</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0.2096219106611607</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.8145751993525046</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.599376731301939</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -38376,6 +38508,15 @@
       <c r="P15" t="n">
         <v>8.206227625669888</v>
       </c>
+      <c r="Q15" t="n">
+        <v>0.2518938665641223</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-0.3845712393142365</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.990799309948246</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -38428,6 +38569,15 @@
       <c r="P16" t="n">
         <v>-12.47645152680662</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0.3261442524676578</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-0.3195769958736814</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.409750367107195</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -38480,6 +38630,15 @@
       <c r="P17" t="n">
         <v>16.39836125436511</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0.4751982762572778</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-1.255769069544986</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.994689131031957</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -38532,6 +38691,15 @@
       <c r="P18" t="n">
         <v>-0.9331506839701568</v>
       </c>
+      <c r="Q18" t="n">
+        <v>0.4088477786862905</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-2.133962066660978</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.460912628227804</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -38584,6 +38752,15 @@
       <c r="P19" t="n">
         <v>3.310226530154257</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0.4396763445978106</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-2.144221873739313</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.37998712998713</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -38636,6 +38813,15 @@
       <c r="P20" t="n">
         <v>0.5449009984294375</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0.4287548138639281</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-1.842826332570251</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.434081829453093</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -38688,6 +38874,15 @@
       <c r="P21" t="n">
         <v>0.7932839339373809</v>
       </c>
+      <c r="Q21" t="n">
+        <v>0.4360175021110002</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.5731976193507933</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.514162395468034</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -38740,6 +38935,15 @@
       <c r="P22" t="n">
         <v>-0.8366510972791943</v>
       </c>
+      <c r="Q22" t="n">
+        <v>0.4864928243129162</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.558428166282324</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.23643949930459</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -38792,6 +38996,15 @@
       <c r="P23" t="n">
         <v>1.144819337733236</v>
       </c>
+      <c r="Q23" t="n">
+        <v>0.4213216419436178</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.4000866350915217</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.023212691436028</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -38844,6 +39057,15 @@
       <c r="P24" t="n">
         <v>0.4545147781253178</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0.418585781447629</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.5004975599582419</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.053709371811689</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -38896,6 +39118,15 @@
       <c r="P25" t="n">
         <v>1.048107739847749</v>
       </c>
+      <c r="Q25" t="n">
+        <v>0.4164115320831739</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3701807772476461</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5.53015873015873</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -38948,6 +39179,15 @@
       <c r="P26" t="n">
         <v>-0.8247021101170733</v>
       </c>
+      <c r="Q26" t="n">
+        <v>0.4935905382956039</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.07165341612992154</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.967634038366946</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -39000,6 +39240,15 @@
       <c r="P27" t="n">
         <v>1.300046048510552</v>
       </c>
+      <c r="Q27" t="n">
+        <v>0.4958841222099098</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.5895287152714498</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.231550742436084</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -39052,6 +39301,15 @@
       <c r="P28" t="n">
         <v>0.5973624366123145</v>
       </c>
+      <c r="Q28" t="n">
+        <v>0.4148978660276161</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.4638349772599782</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.588558711873282</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -39104,6 +39362,15 @@
       <c r="P29" t="n">
         <v>0.5439556491947877</v>
       </c>
+      <c r="Q29" t="n">
+        <v>0.3830070452258044</v>
+      </c>
+      <c r="R29" t="n">
+        <v>-0.03247521200855401</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.896041964711492</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -39156,6 +39423,15 @@
       <c r="P30" t="n">
         <v>-0.8349834099558525</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0.4411661397962768</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.4877219953885864</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6.611146295123496</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -39208,6 +39484,15 @@
       <c r="P31" t="n">
         <v>1.220829541772231</v>
       </c>
+      <c r="Q31" t="n">
+        <v>0.3826530612244898</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-0.2738295202851579</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.372347001854523</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -39260,6 +39545,15 @@
       <c r="P32" t="n">
         <v>0.6438342521972875</v>
       </c>
+      <c r="Q32" t="n">
+        <v>0.3827554464559681</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-0.2286247393755788</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.86412141332701</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -39312,6 +39606,15 @@
       <c r="P33" t="n">
         <v>1.126325749666914</v>
       </c>
+      <c r="Q33" t="n">
+        <v>0.2396851838439439</v>
+      </c>
+      <c r="R33" t="n">
+        <v>-0.1083248262697494</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7.517422867513612</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -39364,6 +39667,15 @@
       <c r="P34" t="n">
         <v>-0.8545591353313093</v>
       </c>
+      <c r="Q34" t="n">
+        <v>0.406251057064574</v>
+      </c>
+      <c r="R34" t="n">
+        <v>-0.6586308214754952</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5.611807137433561</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -39416,6 +39728,15 @@
       <c r="P35" t="n">
         <v>1.531355374343601</v>
       </c>
+      <c r="Q35" t="n">
+        <v>0.419006698694093</v>
+      </c>
+      <c r="R35" t="n">
+        <v>-0.5498267854171545</v>
+      </c>
+      <c r="S35" t="n">
+        <v>7.949973103819258</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -39468,6 +39789,15 @@
       <c r="P36" t="n">
         <v>0.7508897949852706</v>
       </c>
+      <c r="Q36" t="n">
+        <v>0.3765253644137427</v>
+      </c>
+      <c r="R36" t="n">
+        <v>-0.09930356946240228</v>
+      </c>
+      <c r="S36" t="n">
+        <v>18.28658875904285</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -39520,6 +39850,15 @@
       <c r="P37" t="n">
         <v>0.4405191089695979</v>
       </c>
+      <c r="Q37" t="n">
+        <v>0.1935406983672983</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.06921929512464692</v>
+      </c>
+      <c r="S37" t="n">
+        <v>35.33052631578948</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -39572,6 +39911,15 @@
       <c r="P38" t="n">
         <v>-0.7872113355430865</v>
       </c>
+      <c r="Q38" t="n">
+        <v>0.1713265076507651</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-0.06281672781747144</v>
+      </c>
+      <c r="S38" t="n">
+        <v>7.806763285024155</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -39624,6 +39972,15 @@
       <c r="P39" t="n">
         <v>1.422950930318777</v>
       </c>
+      <c r="Q39" t="n">
+        <v>0.2112503560239248</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.2363181681544939</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10.958177278402</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -39675,6 +40032,15 @@
       </c>
       <c r="P40" t="n">
         <v>0.4420892580685389</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.2195957924595202</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.04901118525304422</v>
+      </c>
+      <c r="S40" t="n">
+        <v>16.21657882127456</v>
       </c>
     </row>
   </sheetData>
